--- a/research/traditional_assets/database/data/qatar/qatar_metals_mining.xlsx
+++ b/research/traditional_assets/database/data/qatar/qatar_metals_mining.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="K2">
-        <v>26</v>
+        <v>306.6</v>
       </c>
       <c r="M2">
-        <v>13.3</v>
+        <v>115.3</v>
       </c>
       <c r="N2">
-        <v>0.004817793233355068</v>
+        <v>0.0494892265430509</v>
       </c>
       <c r="O2">
-        <v>0.5115384615384616</v>
+        <v>0.3760600130463144</v>
       </c>
       <c r="P2">
-        <v>13.3</v>
+        <v>115.3</v>
       </c>
       <c r="Q2">
-        <v>0.004817793233355068</v>
+        <v>0.0494892265430509</v>
       </c>
       <c r="R2">
-        <v>0.5115384615384616</v>
+        <v>0.3760600130463144</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -615,31 +615,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>64.09999999999999</v>
+        <v>233.5</v>
       </c>
       <c r="V2">
-        <v>0.02321958994421502</v>
+        <v>0.100223195124045</v>
       </c>
       <c r="W2">
-        <v>0.01655312917807347</v>
+        <v>0.1835488505747127</v>
       </c>
       <c r="X2">
-        <v>0.06163874802810882</v>
+        <v>0.1161477161051399</v>
       </c>
       <c r="Y2">
-        <v>-0.04508561885003536</v>
+        <v>0.06740113446957276</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-0.001841679305642294</v>
+        <v>-0.001721740282100523</v>
       </c>
       <c r="AB2">
-        <v>0.06163874802810882</v>
+        <v>0.1161477161051399</v>
       </c>
       <c r="AC2">
-        <v>-0.06348042733375112</v>
+        <v>-0.1178694563872404</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -651,7 +651,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-64.09999999999999</v>
+        <v>-233.5</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -660,19 +660,19 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.02377155572037827</v>
+        <v>-0.111386728998712</v>
       </c>
       <c r="AK2">
-        <v>-0.04226002109704641</v>
+        <v>-0.1445820433436532</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.681</v>
+        <v>-5.89</v>
       </c>
       <c r="AQ2">
-        <v>4.243759177679882</v>
+        <v>0.4414261460101868</v>
       </c>
     </row>
     <row r="3">
@@ -692,25 +692,25 @@
         </is>
       </c>
       <c r="K3">
-        <v>26</v>
+        <v>306.6</v>
       </c>
       <c r="M3">
-        <v>13.3</v>
+        <v>115.3</v>
       </c>
       <c r="N3">
-        <v>0.004817793233355068</v>
+        <v>0.0494892265430509</v>
       </c>
       <c r="O3">
-        <v>0.5115384615384616</v>
+        <v>0.3760600130463144</v>
       </c>
       <c r="P3">
-        <v>13.3</v>
+        <v>115.3</v>
       </c>
       <c r="Q3">
-        <v>0.004817793233355068</v>
+        <v>0.0494892265430509</v>
       </c>
       <c r="R3">
-        <v>0.5115384615384616</v>
+        <v>0.3760600130463144</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -719,31 +719,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>64.09999999999999</v>
+        <v>233.5</v>
       </c>
       <c r="V3">
-        <v>0.02321958994421502</v>
+        <v>0.100223195124045</v>
       </c>
       <c r="W3">
-        <v>0.01655312917807347</v>
+        <v>0.1835488505747127</v>
       </c>
       <c r="X3">
-        <v>0.06163874802810882</v>
+        <v>0.1161477161051399</v>
       </c>
       <c r="Y3">
-        <v>-0.04508561885003536</v>
+        <v>0.06740113446957276</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>-0.001841679305642294</v>
+        <v>-0.001721740282100523</v>
       </c>
       <c r="AB3">
-        <v>0.06163874802810882</v>
+        <v>0.1161477161051399</v>
       </c>
       <c r="AC3">
-        <v>-0.06348042733375112</v>
+        <v>-0.1178694563872404</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -755,7 +755,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-64.09999999999999</v>
+        <v>-233.5</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -764,19 +764,19 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.02377155572037827</v>
+        <v>-0.111386728998712</v>
       </c>
       <c r="AK3">
-        <v>-0.04226002109704641</v>
+        <v>-0.1445820433436532</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.681</v>
+        <v>-5.89</v>
       </c>
       <c r="AQ3">
-        <v>4.243759177679882</v>
+        <v>0.4414261460101868</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/qatar/qatar_metals_mining.xlsx
+++ b/research/traditional_assets/database/data/qatar/qatar_metals_mining.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="K2">
-        <v>306.6</v>
+        <v>129</v>
       </c>
       <c r="M2">
-        <v>115.3</v>
+        <v>131</v>
       </c>
       <c r="N2">
-        <v>0.0494892265430509</v>
+        <v>0.0610466470944592</v>
       </c>
       <c r="O2">
-        <v>0.3760600130463144</v>
+        <v>1.015503875968992</v>
       </c>
       <c r="P2">
-        <v>115.3</v>
+        <v>131</v>
       </c>
       <c r="Q2">
-        <v>0.0494892265430509</v>
+        <v>0.0610466470944592</v>
       </c>
       <c r="R2">
-        <v>0.3760600130463144</v>
+        <v>1.015503875968992</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -615,31 +615,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>233.5</v>
+        <v>211.1</v>
       </c>
       <c r="V2">
-        <v>0.100223195124045</v>
+        <v>0.09837364276061325</v>
       </c>
       <c r="W2">
-        <v>0.1835488505747127</v>
+        <v>0.06978631322694076</v>
       </c>
       <c r="X2">
-        <v>0.1161477161051399</v>
+        <v>0.09270228373746769</v>
       </c>
       <c r="Y2">
-        <v>0.06740113446957276</v>
+        <v>-0.02291597051052693</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-0.001721740282100523</v>
+        <v>-0.001678018575851393</v>
       </c>
       <c r="AB2">
-        <v>0.1161477161051399</v>
+        <v>0.09270228373746769</v>
       </c>
       <c r="AC2">
-        <v>-0.1178694563872404</v>
+        <v>-0.09438030231331909</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -651,7 +651,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-233.5</v>
+        <v>-211.1</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -660,19 +660,19 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.111386728998712</v>
+        <v>-0.1091068844324995</v>
       </c>
       <c r="AK2">
-        <v>-0.1445820433436532</v>
+        <v>-0.1301238981692658</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-5.89</v>
+        <v>-13.8</v>
       </c>
       <c r="AQ2">
-        <v>0.4414261460101868</v>
+        <v>0.1963768115942029</v>
       </c>
     </row>
     <row r="3">
@@ -692,25 +692,25 @@
         </is>
       </c>
       <c r="K3">
-        <v>306.6</v>
+        <v>129</v>
       </c>
       <c r="M3">
-        <v>115.3</v>
+        <v>131</v>
       </c>
       <c r="N3">
-        <v>0.0494892265430509</v>
+        <v>0.0610466470944592</v>
       </c>
       <c r="O3">
-        <v>0.3760600130463144</v>
+        <v>1.015503875968992</v>
       </c>
       <c r="P3">
-        <v>115.3</v>
+        <v>131</v>
       </c>
       <c r="Q3">
-        <v>0.0494892265430509</v>
+        <v>0.0610466470944592</v>
       </c>
       <c r="R3">
-        <v>0.3760600130463144</v>
+        <v>1.015503875968992</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -719,31 +719,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>233.5</v>
+        <v>211.1</v>
       </c>
       <c r="V3">
-        <v>0.100223195124045</v>
+        <v>0.09837364276061325</v>
       </c>
       <c r="W3">
-        <v>0.1835488505747127</v>
+        <v>0.06978631322694076</v>
       </c>
       <c r="X3">
-        <v>0.1161477161051399</v>
+        <v>0.09270228373746769</v>
       </c>
       <c r="Y3">
-        <v>0.06740113446957276</v>
+        <v>-0.02291597051052693</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>-0.001721740282100523</v>
+        <v>-0.001678018575851393</v>
       </c>
       <c r="AB3">
-        <v>0.1161477161051399</v>
+        <v>0.09270228373746769</v>
       </c>
       <c r="AC3">
-        <v>-0.1178694563872404</v>
+        <v>-0.09438030231331909</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -755,7 +755,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-233.5</v>
+        <v>-211.1</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -764,19 +764,19 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.111386728998712</v>
+        <v>-0.1091068844324995</v>
       </c>
       <c r="AK3">
-        <v>-0.1445820433436532</v>
+        <v>-0.1301238981692658</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-5.89</v>
+        <v>-13.8</v>
       </c>
       <c r="AQ3">
-        <v>0.4414261460101868</v>
+        <v>0.1963768115942029</v>
       </c>
     </row>
   </sheetData>
